--- a/target/test-classes/testdata.xlsx
+++ b/target/test-classes/testdata.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARYASREE\Documents\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE46E768-5D41-4628-AF23-AA40EECE7F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{3FE08982-4ACC-421B-88A0-90B51F762A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{176FB313-24EA-41EF-9071-B8C24219EE85}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{176FB313-24EA-41EF-9071-B8C24219EE85}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
     <sheet name="news" sheetId="2" r:id="rId2"/>
+    <sheet name="contact" sheetId="3" r:id="rId3"/>
+    <sheet name="category" sheetId="4" r:id="rId4"/>
+    <sheet name="footer" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:Q15"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>username</t>
   </si>
@@ -51,16 +49,45 @@
   </si>
   <si>
     <t>50%discount</t>
+  </si>
+  <si>
+    <t>category name</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>sree villa</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>arya@gmail.com</t>
+  </si>
+  <si>
+    <t>phonenumber</t>
+  </si>
+  <si>
+    <t>address</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -83,13 +110,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -463,4 +494,82 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5288E4-A1D8-4DEF-BC23-585B74F4F535}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>43535465645</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>0.625</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE37AE46-E38B-4E76-B782-5FF626B68D29}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18EEB492-5A88-44D5-8BA3-93E0E3AC891E}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>3454656</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{BDE645F0-7AA0-4E0F-B40C-F137975492B0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/target/test-classes/testdata.xlsx
+++ b/target/test-classes/testdata.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{3FE08982-4ACC-421B-88A0-90B51F762A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1B6410AB-8C65-4CB9-9439-F19693A98FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{176FB313-24EA-41EF-9071-B8C24219EE85}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{176FB313-24EA-41EF-9071-B8C24219EE85}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
@@ -19,15 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
